--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_241_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_241_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
         <v>10</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
         <v>16</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,10 +1335,10 @@
         <v>18</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1534,13 +1534,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>3</v>
@@ -1727,7 +1727,7 @@
         <v>15</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2119,7 +2119,7 @@
         <v>14</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>2</v>
@@ -3497,10 +3497,10 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>115</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="V30" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -4292,10 +4292,10 @@
         <v>21</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -4880,10 +4880,10 @@
         <v>9</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>21</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>4</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6252,16 +6252,16 @@
         <v>18</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X45" t="n">
         <v>6</v>
@@ -6784,16 +6784,16 @@
         <v>115</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>27</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_241_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_241_EL.xlsx
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
         <v>10</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>62.50</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>90.00</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -2131,10 +2131,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2327,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -3307,14 +3307,14 @@
         <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>5</v>
       </c>
       <c r="X30" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y40" t="n">
         <v>3</v>
       </c>
-      <c r="Y40" t="n">
-        <v>4</v>
-      </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,10 +5480,10 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6264,10 +6264,10 @@
         <v>3</v>
       </c>
       <c r="X45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="Y48" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="AA48" t="n">
